--- a/Act 1 Laboratory.xlsx
+++ b/Act 1 Laboratory.xlsx
@@ -92,8 +92,22 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
@@ -108,11 +122,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -412,6 +430,7 @@
   <cols>
     <col customWidth="1" min="1" max="9" width="9.5"/>
     <col customWidth="1" min="10" max="10" width="10.5"/>
+    <col customWidth="1" min="12" max="12" width="19.5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -477,6 +496,13 @@
       <c r="J2" s="2">
         <v>100.0</v>
       </c>
+      <c r="L2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4">
+        <f>AVERAGE(A2:J11)</f>
+        <v>111.48</v>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="2">
@@ -509,6 +535,13 @@
       <c r="J3" s="2">
         <v>130.0</v>
       </c>
+      <c r="L3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="4">
+        <f>MEDIAN(A2:J11)</f>
+        <v>111</v>
+      </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="2">
@@ -541,6 +574,13 @@
       <c r="J4" s="2">
         <v>103.0</v>
       </c>
+      <c r="L4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="5">
+        <f>_xlfn.MODE.SNGL(A2:J11)</f>
+        <v>124</v>
+      </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="2">
@@ -573,6 +613,13 @@
       <c r="J5" s="2">
         <v>109.0</v>
       </c>
+      <c r="L5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="4">
+        <f>MAX(A2:J11) - MIN(A2:J11)</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="2">
@@ -605,6 +652,13 @@
       <c r="J6" s="2">
         <v>94.0</v>
       </c>
+      <c r="L6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5">
+        <f>ROUND(_xlfn.VAR.S(A2:J11),2)</f>
+        <v>144.68</v>
+      </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2">
@@ -637,6 +691,13 @@
       <c r="J7" s="2">
         <v>92.0</v>
       </c>
+      <c r="L7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="5">
+        <f>ROUND(STDEV(A2:J11),2)</f>
+        <v>12.03</v>
+      </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="2">
@@ -766,60 +827,12 @@
         <v>92.0</v>
       </c>
     </row>
-    <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4">
-        <f>AVERAGE(A2:J11)</f>
-        <v>111.48</v>
-      </c>
-    </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="4">
-        <f>MEDIAN(A2:J11)</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="5">
-        <f>_xlfn.MODE.SNGL(A2:J11)</f>
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" ht="30.0" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4">
-        <f>MAX(A2:J11) - MIN(A2:J11)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" ht="30.0" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="5">
-        <f>_xlfn.VAR.S(A2:J11)</f>
-        <v>144.6763636</v>
-      </c>
-    </row>
-    <row r="20" ht="45.0" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="5">
-        <f>STDEV(A2:J11)</f>
-        <v>12.0281488</v>
-      </c>
-    </row>
+    <row r="15" ht="30.0" customHeight="1"/>
+    <row r="16" ht="30.0" customHeight="1"/>
+    <row r="17" ht="30.0" customHeight="1"/>
+    <row r="18" ht="30.0" customHeight="1"/>
+    <row r="19" ht="30.0" customHeight="1"/>
+    <row r="20" ht="45.0" customHeight="1"/>
   </sheetData>
   <dataValidations>
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:J11">
